--- a/Diagrams/IMTRA Front Master Sheet.xlsx
+++ b/Diagrams/IMTRA Front Master Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DDrive\Project\Imtra\Imtra_Front_Dev\Diagrams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233A8AF6-1B1A-4F99-B7A2-27C887EE3014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5C255-A1B4-49DF-9341-806A6A0C57EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="857" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="38560" windowHeight="21040" tabRatio="857" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Module" sheetId="1" r:id="rId1"/>
@@ -8953,12 +8953,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8974,12 +8976,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -8987,6 +8991,7 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -9061,81 +9066,94 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="13.5"/>
@@ -9167,6 +9185,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -9189,6 +9208,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -9201,6 +9221,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -9218,18 +9239,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9243,6 +9267,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -9250,17 +9275,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9308,12 +9336,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <strike/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <strike/>
@@ -9335,6 +9365,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="27">
